--- a/Raw_Data/v7a_2050_bio_critical_load.xlsx
+++ b/Raw_Data/v7a_2050_bio_critical_load.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\StefanÅström\C_Verktyg\Python\ALL_PYTHON\2026_v7_Goth_Prot_CBA\Raw_Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{B5041C19-6EC8-4EA3-8C4E-0F61A4E22602}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEB446AF-6FBF-4621-B076-03DEF686304C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-2850" windowWidth="38640" windowHeight="21120" xr2:uid="{6B7B6DF1-0CD8-4246-BFAD-55D047487B99}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6B7B6DF1-0CD8-4246-BFAD-55D047487B99}"/>
   </bookViews>
   <sheets>
     <sheet name="bio_critical_load (11)" sheetId="8" r:id="rId1"/>
@@ -24,7 +24,7 @@
     <sheet name="bio_critical_load (3)" sheetId="5" r:id="rId9"/>
     <sheet name="bio_critical_load (2)" sheetId="3" r:id="rId10"/>
     <sheet name="bio_critical_load (1)" sheetId="2" r:id="rId11"/>
-    <sheet name="bio_critical_load" sheetId="1" r:id="rId12"/>
+    <sheet name="bio_critical_load (13)" sheetId="13" r:id="rId12"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -34,9 +34,6 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1212" uniqueCount="74">
   <si>
     <t>Eutrophication: Exceedance of Critical Loads (all ecosystems)</t>
-  </si>
-  <si>
-    <t>Scenario: LRTAP_Baseline_v7</t>
   </si>
   <si>
     <t xml:space="preserve">Region: </t>
@@ -253,6 +250,9 @@
   </si>
   <si>
     <t>Scenario: OPT Health -60 AAE -40 v7a</t>
+  </si>
+  <si>
+    <t>Scenario: Baseline_v7a</t>
   </si>
 </sst>
 </file>
@@ -1123,73 +1123,73 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
         <v>6</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>7</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>8</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>9</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>10</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>11</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>12</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>13</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
         <v>14</v>
       </c>
-      <c r="L9" t="s">
+      <c r="M9" t="s">
         <v>15</v>
       </c>
-      <c r="M9" t="s">
+      <c r="N9" t="s">
         <v>16</v>
-      </c>
-      <c r="N9" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
         <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
       </c>
       <c r="C10">
         <v>50.5</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11">
         <v>15.6</v>
@@ -1274,10 +1274,10 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C12">
         <v>54.3</v>
@@ -1318,10 +1318,10 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13">
         <v>36.4</v>
@@ -1362,10 +1362,10 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C14">
         <v>1.7</v>
@@ -1406,10 +1406,10 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C15">
         <v>23.8</v>
@@ -1450,10 +1450,10 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C16">
         <v>6.7</v>
@@ -1494,10 +1494,10 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C17">
         <v>30.6</v>
@@ -1538,10 +1538,10 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C18">
         <v>41</v>
@@ -1582,10 +1582,10 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C19">
         <v>176.9</v>
@@ -1626,10 +1626,10 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C20">
         <v>104</v>
@@ -1670,10 +1670,10 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C21">
         <v>77.8</v>
@@ -1714,10 +1714,10 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C22">
         <v>30</v>
@@ -1758,10 +1758,10 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C23">
         <v>16.8</v>
@@ -1802,10 +1802,10 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C24">
         <v>105.8</v>
@@ -1846,10 +1846,10 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C25">
         <v>44.2</v>
@@ -1890,10 +1890,10 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C26">
         <v>26.4</v>
@@ -1934,10 +1934,10 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C27">
         <v>1.4</v>
@@ -1978,10 +1978,10 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -2022,10 +2022,10 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C29">
         <v>3</v>
@@ -2066,10 +2066,10 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C30">
         <v>95.9</v>
@@ -2110,10 +2110,10 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C31">
         <v>42</v>
@@ -2154,10 +2154,10 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B32" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C32">
         <v>109.3</v>
@@ -2198,10 +2198,10 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B33" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C33">
         <v>26.8</v>
@@ -2242,10 +2242,10 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B34" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C34">
         <v>14.1</v>
@@ -2286,10 +2286,10 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B35" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C35">
         <v>251.9</v>
@@ -2330,10 +2330,10 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B36" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C36">
         <v>58.6</v>
@@ -2374,7 +2374,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C37">
         <v>1445.6</v>
@@ -2415,10 +2415,10 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>46</v>
+      </c>
+      <c r="B38" t="s">
         <v>47</v>
-      </c>
-      <c r="B38" t="s">
-        <v>48</v>
       </c>
       <c r="C38">
         <v>20</v>
@@ -2459,10 +2459,10 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C39">
         <v>66.5</v>
@@ -2503,10 +2503,10 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C40">
         <v>37</v>
@@ -2547,10 +2547,10 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C41">
         <v>4.7</v>
@@ -2591,10 +2591,10 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B42" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C42">
         <v>16.899999999999999</v>
@@ -2635,10 +2635,10 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B43" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C43">
         <v>3.8</v>
@@ -2679,10 +2679,10 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C44">
         <v>9.1</v>
@@ -2723,10 +2723,10 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C45">
         <v>303.39999999999998</v>
@@ -2767,10 +2767,10 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C46">
         <v>643.1</v>
@@ -2811,10 +2811,10 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C47">
         <v>33.1</v>
@@ -2855,10 +2855,10 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C48">
         <v>24.2</v>
@@ -2899,10 +2899,10 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B49" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C49">
         <v>97.8</v>
@@ -2943,10 +2943,10 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B50" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C50">
         <v>71.099999999999994</v>
@@ -2987,7 +2987,7 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C51">
         <v>1330.7</v>
@@ -3028,7 +3028,7 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C52">
         <v>2776.2</v>
@@ -3084,73 +3084,73 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
         <v>6</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>7</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>8</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>9</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>10</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>11</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>12</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>13</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
         <v>14</v>
       </c>
-      <c r="L9" t="s">
+      <c r="M9" t="s">
         <v>15</v>
       </c>
-      <c r="M9" t="s">
+      <c r="N9" t="s">
         <v>16</v>
-      </c>
-      <c r="N9" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
         <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
       </c>
       <c r="C10">
         <v>50.5</v>
@@ -3191,10 +3191,10 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11">
         <v>15.6</v>
@@ -3235,10 +3235,10 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C12">
         <v>54.3</v>
@@ -3279,10 +3279,10 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13">
         <v>36.4</v>
@@ -3323,10 +3323,10 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C14">
         <v>1.7</v>
@@ -3367,10 +3367,10 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C15">
         <v>23.8</v>
@@ -3411,10 +3411,10 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C16">
         <v>6.7</v>
@@ -3455,10 +3455,10 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C17">
         <v>30.6</v>
@@ -3499,10 +3499,10 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C18">
         <v>41</v>
@@ -3543,10 +3543,10 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C19">
         <v>176.9</v>
@@ -3587,10 +3587,10 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C20">
         <v>104</v>
@@ -3631,10 +3631,10 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C21">
         <v>77.8</v>
@@ -3675,10 +3675,10 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C22">
         <v>30</v>
@@ -3719,10 +3719,10 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C23">
         <v>16.8</v>
@@ -3763,10 +3763,10 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C24">
         <v>105.8</v>
@@ -3807,10 +3807,10 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C25">
         <v>44.2</v>
@@ -3851,10 +3851,10 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C26">
         <v>26.4</v>
@@ -3895,10 +3895,10 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C27">
         <v>1.4</v>
@@ -3939,10 +3939,10 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -3983,10 +3983,10 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C29">
         <v>3</v>
@@ -4027,10 +4027,10 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C30">
         <v>95.9</v>
@@ -4071,10 +4071,10 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C31">
         <v>42</v>
@@ -4115,10 +4115,10 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B32" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C32">
         <v>109.3</v>
@@ -4159,10 +4159,10 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B33" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C33">
         <v>26.8</v>
@@ -4203,10 +4203,10 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B34" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C34">
         <v>14.1</v>
@@ -4247,10 +4247,10 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B35" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C35">
         <v>251.9</v>
@@ -4291,10 +4291,10 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B36" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C36">
         <v>58.6</v>
@@ -4335,7 +4335,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C37">
         <v>1445.6</v>
@@ -4376,10 +4376,10 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>46</v>
+      </c>
+      <c r="B38" t="s">
         <v>47</v>
-      </c>
-      <c r="B38" t="s">
-        <v>48</v>
       </c>
       <c r="C38">
         <v>20</v>
@@ -4420,10 +4420,10 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C39">
         <v>66.5</v>
@@ -4464,10 +4464,10 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C40">
         <v>37</v>
@@ -4508,10 +4508,10 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C41">
         <v>4.7</v>
@@ -4552,10 +4552,10 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B42" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C42">
         <v>16.899999999999999</v>
@@ -4596,10 +4596,10 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B43" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C43">
         <v>3.8</v>
@@ -4640,10 +4640,10 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C44">
         <v>9.1</v>
@@ -4684,10 +4684,10 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C45">
         <v>303.39999999999998</v>
@@ -4728,10 +4728,10 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C46">
         <v>643.1</v>
@@ -4772,10 +4772,10 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C47">
         <v>33.1</v>
@@ -4816,10 +4816,10 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C48">
         <v>24.2</v>
@@ -4860,10 +4860,10 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B49" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C49">
         <v>97.8</v>
@@ -4904,10 +4904,10 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B50" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C50">
         <v>71.099999999999994</v>
@@ -4948,7 +4948,7 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C51">
         <v>1330.7</v>
@@ -4989,7 +4989,7 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C52">
         <v>2776.2</v>
@@ -5045,73 +5045,73 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
         <v>6</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>7</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>8</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>9</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>10</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>11</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>12</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>13</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
         <v>14</v>
       </c>
-      <c r="L9" t="s">
+      <c r="M9" t="s">
         <v>15</v>
       </c>
-      <c r="M9" t="s">
+      <c r="N9" t="s">
         <v>16</v>
-      </c>
-      <c r="N9" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
         <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
       </c>
       <c r="C10">
         <v>50.5</v>
@@ -5152,10 +5152,10 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11">
         <v>15.6</v>
@@ -5196,10 +5196,10 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C12">
         <v>54.3</v>
@@ -5240,10 +5240,10 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13">
         <v>36.4</v>
@@ -5284,10 +5284,10 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C14">
         <v>1.7</v>
@@ -5328,10 +5328,10 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C15">
         <v>23.8</v>
@@ -5372,10 +5372,10 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C16">
         <v>6.7</v>
@@ -5416,10 +5416,10 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C17">
         <v>30.6</v>
@@ -5460,10 +5460,10 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C18">
         <v>41</v>
@@ -5504,10 +5504,10 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C19">
         <v>176.9</v>
@@ -5548,10 +5548,10 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C20">
         <v>104</v>
@@ -5592,10 +5592,10 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C21">
         <v>77.8</v>
@@ -5636,10 +5636,10 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C22">
         <v>30</v>
@@ -5680,10 +5680,10 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C23">
         <v>16.8</v>
@@ -5724,10 +5724,10 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C24">
         <v>105.8</v>
@@ -5768,10 +5768,10 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C25">
         <v>44.2</v>
@@ -5812,10 +5812,10 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C26">
         <v>26.4</v>
@@ -5856,10 +5856,10 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C27">
         <v>1.4</v>
@@ -5900,10 +5900,10 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -5944,10 +5944,10 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C29">
         <v>3</v>
@@ -5988,10 +5988,10 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C30">
         <v>95.9</v>
@@ -6032,10 +6032,10 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C31">
         <v>42</v>
@@ -6076,10 +6076,10 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B32" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C32">
         <v>109.3</v>
@@ -6120,10 +6120,10 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B33" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C33">
         <v>26.8</v>
@@ -6164,10 +6164,10 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B34" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C34">
         <v>14.1</v>
@@ -6208,10 +6208,10 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B35" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C35">
         <v>251.9</v>
@@ -6252,10 +6252,10 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B36" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C36">
         <v>58.6</v>
@@ -6296,7 +6296,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C37">
         <v>1445.6</v>
@@ -6337,10 +6337,10 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>46</v>
+      </c>
+      <c r="B38" t="s">
         <v>47</v>
-      </c>
-      <c r="B38" t="s">
-        <v>48</v>
       </c>
       <c r="C38">
         <v>20</v>
@@ -6381,10 +6381,10 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C39">
         <v>66.5</v>
@@ -6425,10 +6425,10 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C40">
         <v>37</v>
@@ -6469,10 +6469,10 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C41">
         <v>4.7</v>
@@ -6513,10 +6513,10 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B42" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C42">
         <v>16.899999999999999</v>
@@ -6557,10 +6557,10 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B43" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C43">
         <v>3.8</v>
@@ -6601,10 +6601,10 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C44">
         <v>9.1</v>
@@ -6645,10 +6645,10 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C45">
         <v>303.39999999999998</v>
@@ -6689,10 +6689,10 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C46">
         <v>643.1</v>
@@ -6733,10 +6733,10 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C47">
         <v>33.1</v>
@@ -6777,10 +6777,10 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C48">
         <v>24.2</v>
@@ -6821,10 +6821,10 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B49" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C49">
         <v>97.8</v>
@@ -6865,10 +6865,10 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B50" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C50">
         <v>71.099999999999994</v>
@@ -6909,7 +6909,7 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C51">
         <v>1330.7</v>
@@ -6950,7 +6950,7 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C52">
         <v>2776.2</v>
@@ -6995,7 +6995,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D7A3676-2ED9-40AF-BB1F-640C9FDF0427}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA111733-FB78-4302-90F7-FFAECD43EB03}">
   <dimension ref="A2:N52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -7006,73 +7006,73 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>1</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
         <v>6</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>7</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>8</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>9</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>10</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>11</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>12</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>13</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
         <v>14</v>
       </c>
-      <c r="L9" t="s">
+      <c r="M9" t="s">
         <v>15</v>
       </c>
-      <c r="M9" t="s">
+      <c r="N9" t="s">
         <v>16</v>
-      </c>
-      <c r="N9" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
         <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
       </c>
       <c r="C10">
         <v>50.5</v>
@@ -7113,10 +7113,10 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11">
         <v>15.6</v>
@@ -7157,28 +7157,28 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C12">
         <v>54.3</v>
       </c>
       <c r="D12">
-        <v>75.400000000000006</v>
+        <v>75.599999999999994</v>
       </c>
       <c r="E12">
-        <v>189.2</v>
+        <v>189.5</v>
       </c>
       <c r="F12">
         <v>37.200000000000003</v>
       </c>
       <c r="G12">
-        <v>64.099999999999994</v>
+        <v>64.400000000000006</v>
       </c>
       <c r="H12">
-        <v>95.3</v>
+        <v>95.6</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -7196,15 +7196,15 @@
         <v>100</v>
       </c>
       <c r="N12">
-        <v>393.6</v>
+        <v>394</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13">
         <v>36.4</v>
@@ -7245,10 +7245,10 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C14">
         <v>1.7</v>
@@ -7289,10 +7289,10 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C15">
         <v>23.8</v>
@@ -7333,10 +7333,10 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C16">
         <v>6.7</v>
@@ -7377,10 +7377,10 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C17">
         <v>30.6</v>
@@ -7416,15 +7416,15 @@
         <v>99.4</v>
       </c>
       <c r="N17">
-        <v>99.6</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C18">
         <v>41</v>
@@ -7465,10 +7465,10 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C19">
         <v>176.9</v>
@@ -7509,10 +7509,10 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C20">
         <v>104</v>
@@ -7553,10 +7553,10 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C21">
         <v>77.8</v>
@@ -7565,7 +7565,7 @@
         <v>99.9</v>
       </c>
       <c r="E21">
-        <v>341.4</v>
+        <v>341.6</v>
       </c>
       <c r="F21">
         <v>24.5</v>
@@ -7574,7 +7574,7 @@
         <v>99.8</v>
       </c>
       <c r="H21">
-        <v>334.7</v>
+        <v>334.9</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -7592,15 +7592,15 @@
         <v>100</v>
       </c>
       <c r="N21">
-        <v>344.5</v>
+        <v>344.7</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C22">
         <v>30</v>
@@ -7609,7 +7609,7 @@
         <v>69.8</v>
       </c>
       <c r="E22">
-        <v>325.10000000000002</v>
+        <v>325.2</v>
       </c>
       <c r="F22">
         <v>17.3</v>
@@ -7618,7 +7618,7 @@
         <v>47.8</v>
       </c>
       <c r="H22">
-        <v>161.69999999999999</v>
+        <v>161.80000000000001</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -7636,15 +7636,15 @@
         <v>100</v>
       </c>
       <c r="N22">
-        <v>548.9</v>
+        <v>549.1</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C23">
         <v>16.8</v>
@@ -7685,10 +7685,10 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C24">
         <v>105.8</v>
@@ -7729,28 +7729,28 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C25">
         <v>44.2</v>
       </c>
       <c r="D25">
-        <v>56.3</v>
+        <v>56.2</v>
       </c>
       <c r="E25">
-        <v>93.4</v>
+        <v>92.9</v>
       </c>
       <c r="F25">
         <v>27.1</v>
       </c>
       <c r="G25">
-        <v>28.7</v>
+        <v>28.5</v>
       </c>
       <c r="H25">
-        <v>20</v>
+        <v>19.7</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -7768,15 +7768,15 @@
         <v>100</v>
       </c>
       <c r="N25">
-        <v>209.6</v>
+        <v>208.9</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C26">
         <v>26.4</v>
@@ -7785,16 +7785,16 @@
         <v>90.4</v>
       </c>
       <c r="E26">
-        <v>224.1</v>
+        <v>222.6</v>
       </c>
       <c r="F26">
         <v>18.7</v>
       </c>
       <c r="G26">
-        <v>86.6</v>
+        <v>86.5</v>
       </c>
       <c r="H26">
-        <v>174.3</v>
+        <v>172.7</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -7812,15 +7812,15 @@
         <v>100</v>
       </c>
       <c r="N26">
-        <v>346.6</v>
+        <v>345.6</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C27">
         <v>1.4</v>
@@ -7861,10 +7861,10 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -7905,10 +7905,10 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C29">
         <v>3</v>
@@ -7949,10 +7949,10 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C30">
         <v>95.9</v>
@@ -7961,7 +7961,7 @@
         <v>41.3</v>
       </c>
       <c r="E30">
-        <v>89.9</v>
+        <v>89.8</v>
       </c>
       <c r="F30">
         <v>94.4</v>
@@ -7970,7 +7970,7 @@
         <v>41</v>
       </c>
       <c r="H30">
-        <v>88.5</v>
+        <v>88.4</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -7988,15 +7988,15 @@
         <v>57.1</v>
       </c>
       <c r="N30">
-        <v>177.1</v>
+        <v>176.8</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C31">
         <v>42</v>
@@ -8037,10 +8037,10 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B32" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C32">
         <v>109.3</v>
@@ -8049,7 +8049,7 @@
         <v>89</v>
       </c>
       <c r="E32">
-        <v>275.5</v>
+        <v>276</v>
       </c>
       <c r="F32">
         <v>71.599999999999994</v>
@@ -8058,7 +8058,7 @@
         <v>83.2</v>
       </c>
       <c r="H32">
-        <v>183.2</v>
+        <v>183.7</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -8076,15 +8076,15 @@
         <v>100</v>
       </c>
       <c r="N32">
-        <v>450.2</v>
+        <v>450.8</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B33" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C33">
         <v>26.8</v>
@@ -8093,16 +8093,16 @@
         <v>79.7</v>
       </c>
       <c r="E33">
-        <v>176.1</v>
+        <v>176.2</v>
       </c>
       <c r="F33">
         <v>20.7</v>
       </c>
       <c r="G33">
-        <v>73.599999999999994</v>
+        <v>73.7</v>
       </c>
       <c r="H33">
-        <v>130.80000000000001</v>
+        <v>131</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -8120,21 +8120,21 @@
         <v>100</v>
       </c>
       <c r="N33">
-        <v>328.1</v>
+        <v>328.3</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B34" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C34">
         <v>14.1</v>
       </c>
       <c r="D34">
-        <v>57</v>
+        <v>57.2</v>
       </c>
       <c r="E34">
         <v>195.1</v>
@@ -8143,7 +8143,7 @@
         <v>11</v>
       </c>
       <c r="G34">
-        <v>44.9</v>
+        <v>45.2</v>
       </c>
       <c r="H34">
         <v>112.7</v>
@@ -8164,15 +8164,15 @@
         <v>100</v>
       </c>
       <c r="N34">
-        <v>488.4</v>
+        <v>488.5</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B35" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C35">
         <v>251.9</v>
@@ -8213,10 +8213,10 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B36" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C36">
         <v>58.6</v>
@@ -8257,7 +8257,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C37">
         <v>1445.6</v>
@@ -8266,7 +8266,7 @@
         <v>64</v>
       </c>
       <c r="E37">
-        <v>202.2</v>
+        <v>202.3</v>
       </c>
       <c r="F37">
         <v>927.8</v>
@@ -8298,10 +8298,10 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>46</v>
+      </c>
+      <c r="B38" t="s">
         <v>47</v>
-      </c>
-      <c r="B38" t="s">
-        <v>48</v>
       </c>
       <c r="C38">
         <v>20</v>
@@ -8310,7 +8310,7 @@
         <v>93.5</v>
       </c>
       <c r="E38">
-        <v>369.7</v>
+        <v>369.8</v>
       </c>
       <c r="F38">
         <v>7.4</v>
@@ -8337,15 +8337,15 @@
         <v>100</v>
       </c>
       <c r="N38">
-        <v>479.1</v>
+        <v>479.2</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C39">
         <v>66.5</v>
@@ -8354,7 +8354,7 @@
         <v>100</v>
       </c>
       <c r="E39">
-        <v>485.4</v>
+        <v>474.2</v>
       </c>
       <c r="F39">
         <v>59.6</v>
@@ -8363,7 +8363,7 @@
         <v>100</v>
       </c>
       <c r="H39">
-        <v>476.1</v>
+        <v>464.7</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -8381,15 +8381,15 @@
         <v>100</v>
       </c>
       <c r="N39">
-        <v>566.1</v>
+        <v>557.29999999999995</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C40">
         <v>37</v>
@@ -8407,7 +8407,7 @@
         <v>48.4</v>
       </c>
       <c r="H40">
-        <v>117.9</v>
+        <v>118</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -8425,15 +8425,15 @@
         <v>100</v>
       </c>
       <c r="N40">
-        <v>291.5</v>
+        <v>291.60000000000002</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C41">
         <v>4.7</v>
@@ -8442,7 +8442,7 @@
         <v>76.3</v>
       </c>
       <c r="E41">
-        <v>176.8</v>
+        <v>176.9</v>
       </c>
       <c r="F41">
         <v>4</v>
@@ -8451,7 +8451,7 @@
         <v>71.900000000000006</v>
       </c>
       <c r="H41">
-        <v>138.1</v>
+        <v>138.19999999999999</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -8469,15 +8469,15 @@
         <v>100</v>
       </c>
       <c r="N41">
-        <v>388.7</v>
+        <v>388.8</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B42" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C42">
         <v>16.899999999999999</v>
@@ -8486,7 +8486,7 @@
         <v>69.3</v>
       </c>
       <c r="E42">
-        <v>154.69999999999999</v>
+        <v>154.80000000000001</v>
       </c>
       <c r="F42">
         <v>8.3000000000000007</v>
@@ -8513,15 +8513,15 @@
         <v>100</v>
       </c>
       <c r="N42">
-        <v>274.2</v>
+        <v>274.3</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B43" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C43">
         <v>3.8</v>
@@ -8530,7 +8530,7 @@
         <v>99.8</v>
       </c>
       <c r="E43">
-        <v>386.6</v>
+        <v>393.7</v>
       </c>
       <c r="F43">
         <v>1.8</v>
@@ -8539,7 +8539,7 @@
         <v>99.6</v>
       </c>
       <c r="H43">
-        <v>253.7</v>
+        <v>262</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -8557,15 +8557,15 @@
         <v>100</v>
       </c>
       <c r="N43">
-        <v>511.3</v>
+        <v>517.29999999999995</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C44">
         <v>9.1</v>
@@ -8574,7 +8574,7 @@
         <v>53.3</v>
       </c>
       <c r="E44">
-        <v>115</v>
+        <v>115.1</v>
       </c>
       <c r="F44">
         <v>6.1</v>
@@ -8601,15 +8601,15 @@
         <v>100</v>
       </c>
       <c r="N44">
-        <v>288.7</v>
+        <v>288.8</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C45">
         <v>303.39999999999998</v>
@@ -8627,7 +8627,7 @@
         <v>7.8</v>
       </c>
       <c r="H45">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="I45">
         <v>23.6</v>
@@ -8650,28 +8650,28 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C46">
         <v>643.1</v>
       </c>
       <c r="D46">
-        <v>47.2</v>
+        <v>47.4</v>
       </c>
       <c r="E46">
-        <v>94.5</v>
+        <v>95.9</v>
       </c>
       <c r="F46">
         <v>518.70000000000005</v>
       </c>
       <c r="G46">
-        <v>46.3</v>
+        <v>46.5</v>
       </c>
       <c r="H46">
-        <v>97</v>
+        <v>98.6</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -8686,18 +8686,18 @@
         <v>124.4</v>
       </c>
       <c r="M46">
-        <v>51</v>
+        <v>51.1</v>
       </c>
       <c r="N46">
-        <v>83.7</v>
+        <v>84.5</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C47">
         <v>33.1</v>
@@ -8706,7 +8706,7 @@
         <v>89.6</v>
       </c>
       <c r="E47">
-        <v>420.8</v>
+        <v>420.9</v>
       </c>
       <c r="F47">
         <v>19.8</v>
@@ -8715,7 +8715,7 @@
         <v>82.7</v>
       </c>
       <c r="H47">
-        <v>248.8</v>
+        <v>248.9</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -8733,15 +8733,15 @@
         <v>100</v>
       </c>
       <c r="N47">
-        <v>677.6</v>
+        <v>677.7</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C48">
         <v>24.2</v>
@@ -8782,10 +8782,10 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B49" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C49">
         <v>97.8</v>
@@ -8794,7 +8794,7 @@
         <v>99.9</v>
       </c>
       <c r="E49">
-        <v>460.9</v>
+        <v>463.6</v>
       </c>
       <c r="F49">
         <v>74.5</v>
@@ -8803,7 +8803,7 @@
         <v>99.9</v>
       </c>
       <c r="H49">
-        <v>445.6</v>
+        <v>448.3</v>
       </c>
       <c r="I49">
         <v>0</v>
@@ -8821,15 +8821,15 @@
         <v>100</v>
       </c>
       <c r="N49">
-        <v>509.8</v>
+        <v>512.6</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B50" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C50">
         <v>71.099999999999994</v>
@@ -8870,25 +8870,25 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C51">
         <v>1330.7</v>
       </c>
       <c r="D51">
-        <v>44.9</v>
+        <v>45</v>
       </c>
       <c r="E51">
-        <v>134.69999999999999</v>
+        <v>135.1</v>
       </c>
       <c r="F51">
         <v>877.1</v>
       </c>
       <c r="G51">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
       <c r="H51">
-        <v>145.30000000000001</v>
+        <v>145.69999999999999</v>
       </c>
       <c r="I51">
         <v>24.4</v>
@@ -8897,7 +8897,7 @@
         <v>10.8</v>
       </c>
       <c r="K51">
-        <v>10.3</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="L51">
         <v>429.1</v>
@@ -8906,21 +8906,21 @@
         <v>36.200000000000003</v>
       </c>
       <c r="N51">
-        <v>120.1</v>
+        <v>120.3</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C52">
         <v>2776.2</v>
       </c>
       <c r="D52">
-        <v>54.8</v>
+        <v>54.9</v>
       </c>
       <c r="E52">
-        <v>169.9</v>
+        <v>170</v>
       </c>
       <c r="F52">
         <v>1804.9</v>
@@ -8929,7 +8929,7 @@
         <v>53.3</v>
       </c>
       <c r="H52">
-        <v>157</v>
+        <v>157.19999999999999</v>
       </c>
       <c r="I52">
         <v>32.700000000000003</v>
@@ -8938,7 +8938,7 @@
         <v>10.4</v>
       </c>
       <c r="K52">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="L52">
         <v>938.6</v>
@@ -8947,7 +8947,7 @@
         <v>59.4</v>
       </c>
       <c r="N52">
-        <v>199.9</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -8967,73 +8967,73 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
         <v>6</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>7</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>8</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>9</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>10</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>11</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>12</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>13</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
         <v>14</v>
       </c>
-      <c r="L9" t="s">
+      <c r="M9" t="s">
         <v>15</v>
       </c>
-      <c r="M9" t="s">
+      <c r="N9" t="s">
         <v>16</v>
-      </c>
-      <c r="N9" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
         <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
       </c>
       <c r="C10">
         <v>50.5</v>
@@ -9074,10 +9074,10 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11">
         <v>15.6</v>
@@ -9118,10 +9118,10 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C12">
         <v>54.3</v>
@@ -9162,10 +9162,10 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13">
         <v>36.4</v>
@@ -9206,10 +9206,10 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C14">
         <v>1.7</v>
@@ -9250,10 +9250,10 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C15">
         <v>23.8</v>
@@ -9294,10 +9294,10 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C16">
         <v>6.7</v>
@@ -9338,10 +9338,10 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C17">
         <v>30.6</v>
@@ -9382,10 +9382,10 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C18">
         <v>41</v>
@@ -9426,10 +9426,10 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C19">
         <v>176.9</v>
@@ -9470,10 +9470,10 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C20">
         <v>104</v>
@@ -9514,10 +9514,10 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C21">
         <v>77.8</v>
@@ -9558,10 +9558,10 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C22">
         <v>30</v>
@@ -9602,10 +9602,10 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C23">
         <v>16.8</v>
@@ -9646,10 +9646,10 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C24">
         <v>105.8</v>
@@ -9690,10 +9690,10 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C25">
         <v>44.2</v>
@@ -9734,10 +9734,10 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C26">
         <v>26.4</v>
@@ -9778,10 +9778,10 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C27">
         <v>1.4</v>
@@ -9822,10 +9822,10 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -9866,10 +9866,10 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C29">
         <v>3</v>
@@ -9910,10 +9910,10 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C30">
         <v>95.9</v>
@@ -9954,10 +9954,10 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C31">
         <v>42</v>
@@ -9998,10 +9998,10 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B32" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C32">
         <v>109.3</v>
@@ -10042,10 +10042,10 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B33" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C33">
         <v>26.8</v>
@@ -10086,10 +10086,10 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B34" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C34">
         <v>14.1</v>
@@ -10130,10 +10130,10 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B35" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C35">
         <v>251.9</v>
@@ -10174,10 +10174,10 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B36" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C36">
         <v>58.6</v>
@@ -10218,7 +10218,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C37">
         <v>1445.6</v>
@@ -10259,10 +10259,10 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>46</v>
+      </c>
+      <c r="B38" t="s">
         <v>47</v>
-      </c>
-      <c r="B38" t="s">
-        <v>48</v>
       </c>
       <c r="C38">
         <v>20</v>
@@ -10303,10 +10303,10 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C39">
         <v>66.5</v>
@@ -10347,10 +10347,10 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C40">
         <v>37</v>
@@ -10391,10 +10391,10 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C41">
         <v>4.7</v>
@@ -10435,10 +10435,10 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B42" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C42">
         <v>16.899999999999999</v>
@@ -10479,10 +10479,10 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B43" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C43">
         <v>3.8</v>
@@ -10523,10 +10523,10 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C44">
         <v>9.1</v>
@@ -10567,10 +10567,10 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C45">
         <v>303.39999999999998</v>
@@ -10611,10 +10611,10 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C46">
         <v>643.1</v>
@@ -10655,10 +10655,10 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C47">
         <v>33.1</v>
@@ -10699,10 +10699,10 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C48">
         <v>24.2</v>
@@ -10743,10 +10743,10 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B49" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C49">
         <v>97.8</v>
@@ -10787,10 +10787,10 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B50" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C50">
         <v>71.099999999999994</v>
@@ -10831,7 +10831,7 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C51">
         <v>1330.7</v>
@@ -10872,7 +10872,7 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C52">
         <v>2776.2</v>
@@ -10928,73 +10928,73 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
         <v>6</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>7</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>8</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>9</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>10</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>11</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>12</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>13</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
         <v>14</v>
       </c>
-      <c r="L9" t="s">
+      <c r="M9" t="s">
         <v>15</v>
       </c>
-      <c r="M9" t="s">
+      <c r="N9" t="s">
         <v>16</v>
-      </c>
-      <c r="N9" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
         <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
       </c>
       <c r="C10">
         <v>50.5</v>
@@ -11035,10 +11035,10 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11">
         <v>15.6</v>
@@ -11079,10 +11079,10 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C12">
         <v>54.3</v>
@@ -11123,10 +11123,10 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13">
         <v>36.4</v>
@@ -11167,10 +11167,10 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C14">
         <v>1.7</v>
@@ -11211,10 +11211,10 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C15">
         <v>23.8</v>
@@ -11255,10 +11255,10 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C16">
         <v>6.7</v>
@@ -11299,10 +11299,10 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C17">
         <v>30.6</v>
@@ -11343,10 +11343,10 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C18">
         <v>41</v>
@@ -11387,10 +11387,10 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C19">
         <v>176.9</v>
@@ -11431,10 +11431,10 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C20">
         <v>104</v>
@@ -11475,10 +11475,10 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C21">
         <v>77.8</v>
@@ -11519,10 +11519,10 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C22">
         <v>30</v>
@@ -11563,10 +11563,10 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C23">
         <v>16.8</v>
@@ -11607,10 +11607,10 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C24">
         <v>105.8</v>
@@ -11651,10 +11651,10 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C25">
         <v>44.2</v>
@@ -11695,10 +11695,10 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C26">
         <v>26.4</v>
@@ -11739,10 +11739,10 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C27">
         <v>1.4</v>
@@ -11783,10 +11783,10 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -11827,10 +11827,10 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C29">
         <v>3</v>
@@ -11871,10 +11871,10 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C30">
         <v>95.9</v>
@@ -11915,10 +11915,10 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C31">
         <v>42</v>
@@ -11959,10 +11959,10 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B32" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C32">
         <v>109.3</v>
@@ -12003,10 +12003,10 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B33" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C33">
         <v>26.8</v>
@@ -12047,10 +12047,10 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B34" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C34">
         <v>14.1</v>
@@ -12091,10 +12091,10 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B35" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C35">
         <v>251.9</v>
@@ -12135,10 +12135,10 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B36" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C36">
         <v>58.6</v>
@@ -12179,7 +12179,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C37">
         <v>1445.6</v>
@@ -12220,10 +12220,10 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>46</v>
+      </c>
+      <c r="B38" t="s">
         <v>47</v>
-      </c>
-      <c r="B38" t="s">
-        <v>48</v>
       </c>
       <c r="C38">
         <v>20</v>
@@ -12264,10 +12264,10 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C39">
         <v>66.5</v>
@@ -12308,10 +12308,10 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C40">
         <v>37</v>
@@ -12352,10 +12352,10 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C41">
         <v>4.7</v>
@@ -12396,10 +12396,10 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B42" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C42">
         <v>16.899999999999999</v>
@@ -12440,10 +12440,10 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B43" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C43">
         <v>3.8</v>
@@ -12484,10 +12484,10 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C44">
         <v>9.1</v>
@@ -12528,10 +12528,10 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C45">
         <v>303.39999999999998</v>
@@ -12572,10 +12572,10 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C46">
         <v>643.1</v>
@@ -12616,10 +12616,10 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C47">
         <v>33.1</v>
@@ -12660,10 +12660,10 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C48">
         <v>24.2</v>
@@ -12704,10 +12704,10 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B49" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C49">
         <v>97.8</v>
@@ -12748,10 +12748,10 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B50" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C50">
         <v>71.099999999999994</v>
@@ -12792,7 +12792,7 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C51">
         <v>1330.7</v>
@@ -12833,7 +12833,7 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C52">
         <v>2776.2</v>
@@ -12889,73 +12889,73 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
         <v>6</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>7</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>8</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>9</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>10</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>11</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>12</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>13</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
         <v>14</v>
       </c>
-      <c r="L9" t="s">
+      <c r="M9" t="s">
         <v>15</v>
       </c>
-      <c r="M9" t="s">
+      <c r="N9" t="s">
         <v>16</v>
-      </c>
-      <c r="N9" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
         <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
       </c>
       <c r="C10">
         <v>50.5</v>
@@ -12996,10 +12996,10 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11">
         <v>15.6</v>
@@ -13040,10 +13040,10 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C12">
         <v>54.3</v>
@@ -13084,10 +13084,10 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13">
         <v>36.4</v>
@@ -13128,10 +13128,10 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C14">
         <v>1.7</v>
@@ -13172,10 +13172,10 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C15">
         <v>23.8</v>
@@ -13216,10 +13216,10 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C16">
         <v>6.7</v>
@@ -13260,10 +13260,10 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C17">
         <v>30.6</v>
@@ -13304,10 +13304,10 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C18">
         <v>41</v>
@@ -13348,10 +13348,10 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C19">
         <v>176.9</v>
@@ -13392,10 +13392,10 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C20">
         <v>104</v>
@@ -13436,10 +13436,10 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C21">
         <v>77.8</v>
@@ -13480,10 +13480,10 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C22">
         <v>30</v>
@@ -13524,10 +13524,10 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C23">
         <v>16.8</v>
@@ -13568,10 +13568,10 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C24">
         <v>105.8</v>
@@ -13612,10 +13612,10 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C25">
         <v>44.2</v>
@@ -13656,10 +13656,10 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C26">
         <v>26.4</v>
@@ -13700,10 +13700,10 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C27">
         <v>1.4</v>
@@ -13744,10 +13744,10 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -13788,10 +13788,10 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C29">
         <v>3</v>
@@ -13832,10 +13832,10 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C30">
         <v>95.9</v>
@@ -13876,10 +13876,10 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C31">
         <v>42</v>
@@ -13920,10 +13920,10 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B32" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C32">
         <v>109.3</v>
@@ -13964,10 +13964,10 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B33" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C33">
         <v>26.8</v>
@@ -14008,10 +14008,10 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B34" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C34">
         <v>14.1</v>
@@ -14052,10 +14052,10 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B35" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C35">
         <v>251.9</v>
@@ -14096,10 +14096,10 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B36" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C36">
         <v>58.6</v>
@@ -14140,7 +14140,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C37">
         <v>1445.6</v>
@@ -14181,10 +14181,10 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>46</v>
+      </c>
+      <c r="B38" t="s">
         <v>47</v>
-      </c>
-      <c r="B38" t="s">
-        <v>48</v>
       </c>
       <c r="C38">
         <v>20</v>
@@ -14225,10 +14225,10 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C39">
         <v>66.5</v>
@@ -14269,10 +14269,10 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C40">
         <v>37</v>
@@ -14313,10 +14313,10 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C41">
         <v>4.7</v>
@@ -14357,10 +14357,10 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B42" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C42">
         <v>16.899999999999999</v>
@@ -14401,10 +14401,10 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B43" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C43">
         <v>3.8</v>
@@ -14445,10 +14445,10 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C44">
         <v>9.1</v>
@@ -14489,10 +14489,10 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C45">
         <v>303.39999999999998</v>
@@ -14533,10 +14533,10 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C46">
         <v>643.1</v>
@@ -14577,10 +14577,10 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C47">
         <v>33.1</v>
@@ -14621,10 +14621,10 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C48">
         <v>24.2</v>
@@ -14665,10 +14665,10 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B49" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C49">
         <v>97.8</v>
@@ -14709,10 +14709,10 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B50" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C50">
         <v>71.099999999999994</v>
@@ -14753,7 +14753,7 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C51">
         <v>1330.7</v>
@@ -14794,7 +14794,7 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C52">
         <v>2776.2</v>
@@ -14850,73 +14850,73 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
         <v>6</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>7</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>8</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>9</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>10</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>11</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>12</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>13</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
         <v>14</v>
       </c>
-      <c r="L9" t="s">
+      <c r="M9" t="s">
         <v>15</v>
       </c>
-      <c r="M9" t="s">
+      <c r="N9" t="s">
         <v>16</v>
-      </c>
-      <c r="N9" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
         <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
       </c>
       <c r="C10">
         <v>50.5</v>
@@ -14957,10 +14957,10 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11">
         <v>15.6</v>
@@ -15001,10 +15001,10 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C12">
         <v>54.3</v>
@@ -15045,10 +15045,10 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13">
         <v>36.4</v>
@@ -15089,10 +15089,10 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C14">
         <v>1.7</v>
@@ -15133,10 +15133,10 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C15">
         <v>23.8</v>
@@ -15177,10 +15177,10 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C16">
         <v>6.7</v>
@@ -15221,10 +15221,10 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C17">
         <v>30.6</v>
@@ -15265,10 +15265,10 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C18">
         <v>41</v>
@@ -15309,10 +15309,10 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C19">
         <v>176.9</v>
@@ -15353,10 +15353,10 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C20">
         <v>104</v>
@@ -15397,10 +15397,10 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C21">
         <v>77.8</v>
@@ -15441,10 +15441,10 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C22">
         <v>30</v>
@@ -15485,10 +15485,10 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C23">
         <v>16.8</v>
@@ -15529,10 +15529,10 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C24">
         <v>105.8</v>
@@ -15573,10 +15573,10 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C25">
         <v>44.2</v>
@@ -15617,10 +15617,10 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C26">
         <v>26.4</v>
@@ -15661,10 +15661,10 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C27">
         <v>1.4</v>
@@ -15705,10 +15705,10 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -15749,10 +15749,10 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C29">
         <v>3</v>
@@ -15793,10 +15793,10 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C30">
         <v>95.9</v>
@@ -15837,10 +15837,10 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C31">
         <v>42</v>
@@ -15881,10 +15881,10 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B32" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C32">
         <v>109.3</v>
@@ -15925,10 +15925,10 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B33" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C33">
         <v>26.8</v>
@@ -15969,10 +15969,10 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B34" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C34">
         <v>14.1</v>
@@ -16013,10 +16013,10 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B35" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C35">
         <v>251.9</v>
@@ -16057,10 +16057,10 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B36" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C36">
         <v>58.6</v>
@@ -16101,7 +16101,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C37">
         <v>1445.6</v>
@@ -16142,10 +16142,10 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>46</v>
+      </c>
+      <c r="B38" t="s">
         <v>47</v>
-      </c>
-      <c r="B38" t="s">
-        <v>48</v>
       </c>
       <c r="C38">
         <v>20</v>
@@ -16186,10 +16186,10 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C39">
         <v>66.5</v>
@@ -16230,10 +16230,10 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C40">
         <v>37</v>
@@ -16274,10 +16274,10 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C41">
         <v>4.7</v>
@@ -16318,10 +16318,10 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B42" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C42">
         <v>16.899999999999999</v>
@@ -16362,10 +16362,10 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B43" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C43">
         <v>3.8</v>
@@ -16406,10 +16406,10 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C44">
         <v>9.1</v>
@@ -16450,10 +16450,10 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C45">
         <v>303.39999999999998</v>
@@ -16494,10 +16494,10 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C46">
         <v>643.1</v>
@@ -16538,10 +16538,10 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C47">
         <v>33.1</v>
@@ -16582,10 +16582,10 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C48">
         <v>24.2</v>
@@ -16626,10 +16626,10 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B49" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C49">
         <v>97.8</v>
@@ -16670,10 +16670,10 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B50" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C50">
         <v>71.099999999999994</v>
@@ -16714,7 +16714,7 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C51">
         <v>1330.7</v>
@@ -16755,7 +16755,7 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C52">
         <v>2776.2</v>
@@ -16811,73 +16811,73 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
         <v>6</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>7</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>8</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>9</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>10</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>11</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>12</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>13</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
         <v>14</v>
       </c>
-      <c r="L9" t="s">
+      <c r="M9" t="s">
         <v>15</v>
       </c>
-      <c r="M9" t="s">
+      <c r="N9" t="s">
         <v>16</v>
-      </c>
-      <c r="N9" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
         <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
       </c>
       <c r="C10">
         <v>50.5</v>
@@ -16918,10 +16918,10 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11">
         <v>15.6</v>
@@ -16962,10 +16962,10 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C12">
         <v>54.3</v>
@@ -17006,10 +17006,10 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13">
         <v>36.4</v>
@@ -17050,10 +17050,10 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C14">
         <v>1.7</v>
@@ -17094,10 +17094,10 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C15">
         <v>23.8</v>
@@ -17138,10 +17138,10 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C16">
         <v>6.7</v>
@@ -17182,10 +17182,10 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C17">
         <v>30.6</v>
@@ -17226,10 +17226,10 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C18">
         <v>41</v>
@@ -17270,10 +17270,10 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C19">
         <v>176.9</v>
@@ -17314,10 +17314,10 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C20">
         <v>104</v>
@@ -17358,10 +17358,10 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C21">
         <v>77.8</v>
@@ -17402,10 +17402,10 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C22">
         <v>30</v>
@@ -17446,10 +17446,10 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C23">
         <v>16.8</v>
@@ -17490,10 +17490,10 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C24">
         <v>105.8</v>
@@ -17534,10 +17534,10 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C25">
         <v>44.2</v>
@@ -17578,10 +17578,10 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C26">
         <v>26.4</v>
@@ -17622,10 +17622,10 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C27">
         <v>1.4</v>
@@ -17666,10 +17666,10 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -17710,10 +17710,10 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C29">
         <v>3</v>
@@ -17754,10 +17754,10 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C30">
         <v>95.9</v>
@@ -17798,10 +17798,10 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C31">
         <v>42</v>
@@ -17842,10 +17842,10 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B32" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C32">
         <v>109.3</v>
@@ -17886,10 +17886,10 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B33" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C33">
         <v>26.8</v>
@@ -17930,10 +17930,10 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B34" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C34">
         <v>14.1</v>
@@ -17974,10 +17974,10 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B35" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C35">
         <v>251.9</v>
@@ -18018,10 +18018,10 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B36" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C36">
         <v>58.6</v>
@@ -18062,7 +18062,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C37">
         <v>1445.6</v>
@@ -18103,10 +18103,10 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>46</v>
+      </c>
+      <c r="B38" t="s">
         <v>47</v>
-      </c>
-      <c r="B38" t="s">
-        <v>48</v>
       </c>
       <c r="C38">
         <v>20</v>
@@ -18147,10 +18147,10 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C39">
         <v>66.5</v>
@@ -18191,10 +18191,10 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C40">
         <v>37</v>
@@ -18235,10 +18235,10 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C41">
         <v>4.7</v>
@@ -18279,10 +18279,10 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B42" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C42">
         <v>16.899999999999999</v>
@@ -18323,10 +18323,10 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B43" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C43">
         <v>3.8</v>
@@ -18367,10 +18367,10 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C44">
         <v>9.1</v>
@@ -18411,10 +18411,10 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C45">
         <v>303.39999999999998</v>
@@ -18455,10 +18455,10 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C46">
         <v>643.1</v>
@@ -18499,10 +18499,10 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C47">
         <v>33.1</v>
@@ -18543,10 +18543,10 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C48">
         <v>24.2</v>
@@ -18587,10 +18587,10 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B49" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C49">
         <v>97.8</v>
@@ -18631,10 +18631,10 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B50" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C50">
         <v>71.099999999999994</v>
@@ -18675,7 +18675,7 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C51">
         <v>1330.7</v>
@@ -18716,7 +18716,7 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C52">
         <v>2776.2</v>
@@ -18772,73 +18772,73 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
         <v>6</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>7</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>8</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>9</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>10</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>11</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>12</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>13</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
         <v>14</v>
       </c>
-      <c r="L9" t="s">
+      <c r="M9" t="s">
         <v>15</v>
       </c>
-      <c r="M9" t="s">
+      <c r="N9" t="s">
         <v>16</v>
-      </c>
-      <c r="N9" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
         <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
       </c>
       <c r="C10">
         <v>50.5</v>
@@ -18879,10 +18879,10 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11">
         <v>15.6</v>
@@ -18923,10 +18923,10 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C12">
         <v>54.3</v>
@@ -18967,10 +18967,10 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13">
         <v>36.4</v>
@@ -19011,10 +19011,10 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C14">
         <v>1.7</v>
@@ -19055,10 +19055,10 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C15">
         <v>23.8</v>
@@ -19099,10 +19099,10 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C16">
         <v>6.7</v>
@@ -19143,10 +19143,10 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C17">
         <v>30.6</v>
@@ -19187,10 +19187,10 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C18">
         <v>41</v>
@@ -19231,10 +19231,10 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C19">
         <v>176.9</v>
@@ -19275,10 +19275,10 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C20">
         <v>104</v>
@@ -19319,10 +19319,10 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C21">
         <v>77.8</v>
@@ -19363,10 +19363,10 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C22">
         <v>30</v>
@@ -19407,10 +19407,10 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C23">
         <v>16.8</v>
@@ -19451,10 +19451,10 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C24">
         <v>105.8</v>
@@ -19495,10 +19495,10 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C25">
         <v>44.2</v>
@@ -19539,10 +19539,10 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C26">
         <v>26.4</v>
@@ -19583,10 +19583,10 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C27">
         <v>1.4</v>
@@ -19627,10 +19627,10 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -19671,10 +19671,10 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C29">
         <v>3</v>
@@ -19715,10 +19715,10 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C30">
         <v>95.9</v>
@@ -19759,10 +19759,10 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C31">
         <v>42</v>
@@ -19803,10 +19803,10 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B32" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C32">
         <v>109.3</v>
@@ -19847,10 +19847,10 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B33" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C33">
         <v>26.8</v>
@@ -19891,10 +19891,10 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B34" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C34">
         <v>14.1</v>
@@ -19935,10 +19935,10 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B35" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C35">
         <v>251.9</v>
@@ -19979,10 +19979,10 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B36" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C36">
         <v>58.6</v>
@@ -20023,7 +20023,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C37">
         <v>1445.6</v>
@@ -20064,10 +20064,10 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>46</v>
+      </c>
+      <c r="B38" t="s">
         <v>47</v>
-      </c>
-      <c r="B38" t="s">
-        <v>48</v>
       </c>
       <c r="C38">
         <v>20</v>
@@ -20108,10 +20108,10 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C39">
         <v>66.5</v>
@@ -20152,10 +20152,10 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C40">
         <v>37</v>
@@ -20196,10 +20196,10 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C41">
         <v>4.7</v>
@@ -20240,10 +20240,10 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B42" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C42">
         <v>16.899999999999999</v>
@@ -20284,10 +20284,10 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B43" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C43">
         <v>3.8</v>
@@ -20328,10 +20328,10 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C44">
         <v>9.1</v>
@@ -20372,10 +20372,10 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C45">
         <v>303.39999999999998</v>
@@ -20416,10 +20416,10 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C46">
         <v>643.1</v>
@@ -20460,10 +20460,10 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C47">
         <v>33.1</v>
@@ -20504,10 +20504,10 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C48">
         <v>24.2</v>
@@ -20548,10 +20548,10 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B49" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C49">
         <v>97.8</v>
@@ -20592,10 +20592,10 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B50" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C50">
         <v>71.099999999999994</v>
@@ -20636,7 +20636,7 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C51">
         <v>1330.7</v>
@@ -20677,7 +20677,7 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C52">
         <v>2776.2</v>
@@ -20733,73 +20733,73 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
         <v>6</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>7</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>8</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>9</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>10</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>11</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>12</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>13</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
         <v>14</v>
       </c>
-      <c r="L9" t="s">
+      <c r="M9" t="s">
         <v>15</v>
       </c>
-      <c r="M9" t="s">
+      <c r="N9" t="s">
         <v>16</v>
-      </c>
-      <c r="N9" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
         <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
       </c>
       <c r="C10">
         <v>50.5</v>
@@ -20840,10 +20840,10 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11">
         <v>15.6</v>
@@ -20884,10 +20884,10 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C12">
         <v>54.3</v>
@@ -20928,10 +20928,10 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13">
         <v>36.4</v>
@@ -20972,10 +20972,10 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C14">
         <v>1.7</v>
@@ -21016,10 +21016,10 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C15">
         <v>23.8</v>
@@ -21060,10 +21060,10 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C16">
         <v>6.7</v>
@@ -21104,10 +21104,10 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C17">
         <v>30.6</v>
@@ -21148,10 +21148,10 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C18">
         <v>41</v>
@@ -21192,10 +21192,10 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C19">
         <v>176.9</v>
@@ -21236,10 +21236,10 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C20">
         <v>104</v>
@@ -21280,10 +21280,10 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C21">
         <v>77.8</v>
@@ -21324,10 +21324,10 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C22">
         <v>30</v>
@@ -21368,10 +21368,10 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C23">
         <v>16.8</v>
@@ -21412,10 +21412,10 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C24">
         <v>105.8</v>
@@ -21456,10 +21456,10 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C25">
         <v>44.2</v>
@@ -21500,10 +21500,10 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C26">
         <v>26.4</v>
@@ -21544,10 +21544,10 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C27">
         <v>1.4</v>
@@ -21588,10 +21588,10 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -21632,10 +21632,10 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C29">
         <v>3</v>
@@ -21676,10 +21676,10 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C30">
         <v>95.9</v>
@@ -21720,10 +21720,10 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C31">
         <v>42</v>
@@ -21764,10 +21764,10 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B32" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C32">
         <v>109.3</v>
@@ -21808,10 +21808,10 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B33" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C33">
         <v>26.8</v>
@@ -21852,10 +21852,10 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B34" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C34">
         <v>14.1</v>
@@ -21896,10 +21896,10 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B35" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C35">
         <v>251.9</v>
@@ -21940,10 +21940,10 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B36" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C36">
         <v>58.6</v>
@@ -21984,7 +21984,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C37">
         <v>1445.6</v>
@@ -22025,10 +22025,10 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>46</v>
+      </c>
+      <c r="B38" t="s">
         <v>47</v>
-      </c>
-      <c r="B38" t="s">
-        <v>48</v>
       </c>
       <c r="C38">
         <v>20</v>
@@ -22069,10 +22069,10 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C39">
         <v>66.5</v>
@@ -22113,10 +22113,10 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C40">
         <v>37</v>
@@ -22157,10 +22157,10 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C41">
         <v>4.7</v>
@@ -22201,10 +22201,10 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B42" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C42">
         <v>16.899999999999999</v>
@@ -22245,10 +22245,10 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B43" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C43">
         <v>3.8</v>
@@ -22289,10 +22289,10 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C44">
         <v>9.1</v>
@@ -22333,10 +22333,10 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C45">
         <v>303.39999999999998</v>
@@ -22377,10 +22377,10 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C46">
         <v>643.1</v>
@@ -22421,10 +22421,10 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C47">
         <v>33.1</v>
@@ -22465,10 +22465,10 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C48">
         <v>24.2</v>
@@ -22509,10 +22509,10 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B49" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C49">
         <v>97.8</v>
@@ -22553,10 +22553,10 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B50" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C50">
         <v>71.099999999999994</v>
@@ -22597,7 +22597,7 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C51">
         <v>1330.7</v>
@@ -22638,7 +22638,7 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C52">
         <v>2776.2</v>
@@ -22694,73 +22694,73 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
         <v>6</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>7</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>8</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>9</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>10</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>11</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>12</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>13</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
         <v>14</v>
       </c>
-      <c r="L9" t="s">
+      <c r="M9" t="s">
         <v>15</v>
       </c>
-      <c r="M9" t="s">
+      <c r="N9" t="s">
         <v>16</v>
-      </c>
-      <c r="N9" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
         <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
       </c>
       <c r="C10">
         <v>50.5</v>
@@ -22801,10 +22801,10 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11">
         <v>15.6</v>
@@ -22845,10 +22845,10 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C12">
         <v>54.3</v>
@@ -22889,10 +22889,10 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13">
         <v>36.4</v>
@@ -22933,10 +22933,10 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C14">
         <v>1.7</v>
@@ -22977,10 +22977,10 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C15">
         <v>23.8</v>
@@ -23021,10 +23021,10 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C16">
         <v>6.7</v>
@@ -23065,10 +23065,10 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C17">
         <v>30.6</v>
@@ -23109,10 +23109,10 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C18">
         <v>41</v>
@@ -23153,10 +23153,10 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C19">
         <v>176.9</v>
@@ -23197,10 +23197,10 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C20">
         <v>104</v>
@@ -23241,10 +23241,10 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C21">
         <v>77.8</v>
@@ -23285,10 +23285,10 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C22">
         <v>30</v>
@@ -23329,10 +23329,10 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C23">
         <v>16.8</v>
@@ -23373,10 +23373,10 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C24">
         <v>105.8</v>
@@ -23417,10 +23417,10 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C25">
         <v>44.2</v>
@@ -23461,10 +23461,10 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C26">
         <v>26.4</v>
@@ -23505,10 +23505,10 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C27">
         <v>1.4</v>
@@ -23549,10 +23549,10 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -23593,10 +23593,10 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C29">
         <v>3</v>
@@ -23637,10 +23637,10 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C30">
         <v>95.9</v>
@@ -23681,10 +23681,10 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C31">
         <v>42</v>
@@ -23725,10 +23725,10 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B32" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C32">
         <v>109.3</v>
@@ -23769,10 +23769,10 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B33" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C33">
         <v>26.8</v>
@@ -23813,10 +23813,10 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B34" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C34">
         <v>14.1</v>
@@ -23857,10 +23857,10 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B35" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C35">
         <v>251.9</v>
@@ -23901,10 +23901,10 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B36" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C36">
         <v>58.6</v>
@@ -23945,7 +23945,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C37">
         <v>1445.6</v>
@@ -23986,10 +23986,10 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>46</v>
+      </c>
+      <c r="B38" t="s">
         <v>47</v>
-      </c>
-      <c r="B38" t="s">
-        <v>48</v>
       </c>
       <c r="C38">
         <v>20</v>
@@ -24030,10 +24030,10 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C39">
         <v>66.5</v>
@@ -24074,10 +24074,10 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C40">
         <v>37</v>
@@ -24118,10 +24118,10 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C41">
         <v>4.7</v>
@@ -24162,10 +24162,10 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B42" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C42">
         <v>16.899999999999999</v>
@@ -24206,10 +24206,10 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B43" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C43">
         <v>3.8</v>
@@ -24250,10 +24250,10 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C44">
         <v>9.1</v>
@@ -24294,10 +24294,10 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C45">
         <v>303.39999999999998</v>
@@ -24338,10 +24338,10 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C46">
         <v>643.1</v>
@@ -24382,10 +24382,10 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C47">
         <v>33.1</v>
@@ -24426,10 +24426,10 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C48">
         <v>24.2</v>
@@ -24470,10 +24470,10 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B49" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C49">
         <v>97.8</v>
@@ -24514,10 +24514,10 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B50" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C50">
         <v>71.099999999999994</v>
@@ -24558,7 +24558,7 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C51">
         <v>1330.7</v>
@@ -24599,7 +24599,7 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C52">
         <v>2776.2</v>
